--- a/docs/in-progress.xlsx
+++ b/docs/in-progress.xlsx
@@ -1,9 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookViews>
-    <workbookView/>
-  </workbookViews>
   <sheets>
     <sheet name="In Progress" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -15,7 +12,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +46,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -487,12 +483,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Workspace Provisioning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Founder lock and workspace-scoped admin boundaries started</t>
+          <t>Invite acceptance flow for seeded users implemented</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -512,34 +508,34 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Role boundaries now exist in admin flows, but action-level RBAC is not complete</t>
+          <t>Invite issuance, lookup, re-invite, and signup completion now exist locally</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Extend into module-by-module permission enforcement</t>
+          <t>Deploy and smoke-test stakeholder onboarding flow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Phase 8</t>
+          <t>Phase 12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Tenant Lifecycle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HR API routes added (employees, payroll, attendance, positions)</t>
+          <t>Founder lock and workspace-scoped admin boundaries started</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -559,12 +555,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Routes exist in local worktree</t>
+          <t>Role boundaries now exist in admin flows, but action-level RBAC is not complete</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Extend into module-by-module permission enforcement</t>
         </is>
       </c>
     </row>
@@ -581,12 +577,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HR page rewritten to call /api/hr/*</t>
+          <t>HR API routes added (employees, payroll, attendance, positions)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -606,12 +602,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>UI is being moved off mock/local-only state</t>
+          <t>Routes exist in local worktree</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -628,12 +624,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HR scorecard/compliance views present</t>
+          <t>HR page rewritten to call /api/hr/*</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -648,17 +644,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Support components exist locally</t>
+          <t>UI is being moved off mock/local-only state</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Finish polish and validation</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -670,17 +666,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Data Quality</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projects API routes added</t>
+          <t>HR scorecard/compliance views present</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -695,17 +691,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>/api/projects and /api/projects/tasks exist locally</t>
+          <t>Support components exist locally</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Finish polish and validation</t>
         </is>
       </c>
     </row>
@@ -722,12 +718,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Projects page rewritten to use live API</t>
+          <t>Projects API routes added</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -747,12 +743,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Project board/task/timeline are wired toward live data</t>
+          <t>/api/projects and /api/projects/tasks exist locally</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -764,17 +760,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Inventory API routes added</t>
+          <t>Projects page rewritten to use live API</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -794,12 +790,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Products, stock, orders routes exist locally</t>
+          <t>Project board/task/timeline are wired toward live data</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -816,12 +812,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Inventory page rewritten to use live API</t>
+          <t>Inventory API routes added</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -841,12 +837,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tables are wired toward live data</t>
+          <t>Products, stock, orders routes exist locally</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -858,17 +854,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shared Backend</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seed Data</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Module seed helper added for HR/Projects/Inventory</t>
+          <t>Inventory page rewritten to use live API</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -883,17 +879,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Local seed helper exists</t>
+          <t>Tables are wired toward live data</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Keep only as controlled dev/demo behavior</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -910,12 +906,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Seed Data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Org ownership checks added to new HR/Projects/Inventory routes</t>
+          <t>Module seed helper added for HR/Projects/Inventory</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -930,62 +926,109 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mutation routes were tightened locally</t>
+          <t>Local seed helper exists</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ship with backend conversion commit</t>
+          <t>Keep only as controlled dev/demo behavior</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Phase 8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Shared Backend</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Org ownership checks added to new HR/Projects/Inventory routes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Local only</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mutation routes were tightened locally</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ship with backend conversion commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Phase 9</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Pending migration created for HR/Projects/Inventory backend</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Local only</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Local only</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Migration folder exists locally</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Apply migration to active database</t>
         </is>
